--- a/public/templates/import-spese-template.xlsx
+++ b/public/templates/import-spese-template.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -130,20 +130,15 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Pagamento automatico</t>
+          <t>Ricorrente</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Ricorrente</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
         <is>
           <t>Note fornitore</t>
         </is>
@@ -266,15 +261,10 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Riga di esempio modificabile</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
-        <is>
-          <t>Riga di esempio modificabile</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
         <is>
           <t>Note interne fornitore</t>
         </is>
